--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0056.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0056.xlsx
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Vị {Male=quý ông;Female=quý cô} đây đã giải được câu đố. Giờ ta sẽ cùng {Male=ông ấy;Female=bà ấy} chế tạo thuốc hồi sinh.</t>
+          <t>Vị {Male=he;Female=she} đây đã giải được câu đố. Giờ ta sẽ cùng {Male=he;Female=she} chế tạo thuốc hồi sinh.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Còn lá thư ta nhận được thì sao?</t>
+          <t>Còn lá thư tao nhận được thì sao?</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Còn ảnh hưởng lên ta thì sao?</t>
+          <t>Còn ảnh hưởng lên tao thì sao?</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Ta sẽ giúp đến khi mọi chuyện được giải quyết.</t>
+          <t>Tao sẽ giúp đến khi mọi chuyện được giải quyết.</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Đây vẫn là Lâu đài Porto-Veno chứ? Có gì đó... không ổn.</t>
+          <t>Đây vẫn là Porto-Veno Castle chứ? Có gì đó... không ổn.</t>
         </is>
       </c>
     </row>
@@ -13058,7 +13058,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Ta đã thấy sức nặng của những gì cô ấy hy sinh cho thử thách đó, tất cả chỉ vì một lý tưởng chẳng xứng đáng với sự hy sinh của cô ấy chút nào.</t>
+          <t>Tao đã thấy sức nặng của những gì cô ấy hy sinh cho thử thách đó, tất cả chỉ vì một lý tưởng chẳng xứng đáng với sự hy sinh của cô ấy chút nào.</t>
         </is>
       </c>
     </row>
@@ -17805,7 +17805,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Cậu ổn chứ?</t>
+          <t>Cậu ổn không?</t>
         </is>
       </c>
     </row>
